--- a/tests/sample_artifacts/invalid/excel/invalid_additional_unknown_columns.xlsx
+++ b/tests/sample_artifacts/invalid/excel/invalid_additional_unknown_columns.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Customers_AU" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Customers_US" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +50,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,10 +444,25 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>IsActive</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>RegionCode</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>SourceSystem</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>UnexpectedCode</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ProcessName</t>
         </is>
@@ -451,7 +471,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CUST82001</t>
+          <t>CUST01100</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -459,50 +479,351 @@
           <t>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2025-02-01</t>
-        </is>
+      <c r="C2" s="1" t="n">
+        <v>45299</v>
       </c>
       <c r="D2" t="n">
-        <v>1500.25</v>
+        <v>1550</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>UNMAPPED_001</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>does_not_exist</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CUST01101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Customer 1101</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>not-a-date</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1585.75</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>UNMAPPED_002</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>does_not_exist</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CUST01102</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Customer 1102</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>45301</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>BAD_NUMBER</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>UNMAPPED_003</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>does_not_exist</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CUST01103</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Customer 1103</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>45302</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1657.25</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>UNMAPPED_004</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>does_not_exist</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>CustomerId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>CustomerName</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>SignupDate</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>CreditLimit</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>IsActive</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>RegionCode</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>SourceSystem</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CUST02100</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Customer 2100</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>45299</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1550</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>does_not_exist</t>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CRM</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CUST02101</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Missing Key</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>not-a-date</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>BAD_NUMBER</t>
-        </is>
+          <t>Customer 2101</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>45300</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1585.75</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UNMAPPED_002</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>does_not_exist</t>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CUST02102</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Customer 2102</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>45301</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1621.5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CUST02103</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Customer 2103</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>45302</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1657.25</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CRM</t>
         </is>
       </c>
     </row>
